--- a/Result/checksun_f/2026-01-18.xlsx
+++ b/Result/checksun_f/2026-01-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW1"/>
+  <dimension ref="A1:CX1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,11 @@
       <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>盤整震盪_前15日次數</t>
         </is>
       </c>
     </row>
